--- a/hpi_scraper/Technographic/theirstack/theirstack_data.xlsx
+++ b/hpi_scraper/Technographic/theirstack/theirstack_data.xlsx
@@ -445,7 +445,7 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
@@ -500,27 +500,27 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Python; Microsoft Azure; Amazon Web Services; Java; Microsoft Powerpoint; Microsoft Excel; SAP; Jira; Kubernetes; Ansible; Power BI; Oracle; JavaScript; Spring Boot; Confluence; Provide Support; Spring; Jenkins; Streamline; ServiceNow.com; AWS IoT; Microsoft Forefront; Node.js; MongoDB; Red Hat; AWS Managed Services; React; PowerShell; ELK; Microsoft Active Directory; Apache Maven; Active Directory; Fortinet; OpenStack; Apache Spark; Salesforce; Grafana; Root Cause; Yarn; Prometheus; Elasticsearch; Redis; SonarQube; NGINX; J2EE; Network Solutions; MSSQL; Windows Server; TypeScript; SAP Ariba; Dynatrace; Microsoft Hyper-V; Google Surveys; Workspace; Apigee; Webpack; eLearning LMS; JBoss; GuardRails; Figma; Apache Camel; Airflow; Nutanix; Apache Airflow; Processing; Amazon CloudWatch; AWS Auto Scaling; Superhuman; Amazon S3; Macro; Silver Peak; KVM; Microsoft Visio; Bootstrap; F5; Amazon RDS; LangChain; Cucumber; Azure Stack; VeloCloud; JSON API; Zabbix; Selenium; C#; Google Analytics; Splunk; Sanity; Soap UI; Ivalua; Microsoft Teams; TensorFlow; Helm; Microsoft Power Apps; SAP S/4HANA (SAP Cloud ERP); NVIDIA; Amdocs; Kong; Elastic; Benchmark; Microsoft Power Platform; AWS Data Exchange; React Native; CRD; AWS Command Line Interface; SAP SuccessFactors; Istio; Adobe Experience Manager; Microsoft Project; Successfactors; Google VPC; Microsoft SharePoint; Review Board; Envoy; SailPoint; AWS Mobile Services; Microsoft Outlook; Runbook; SAP FICO; Radware; Control-M; Azure Active Directory; Vault; Catalyst; Red Hat OpenShift; Tagetik; Symantec; Viptela; Xpand; Oracle Database; Cisco Routers; Launchpad; Attribution; Sharpen; Intel; Sungard; Delta Lake; Microsoft Exchange Online; Argo; Miro; Crossplane; HashiCorp; Cisco Jasper; Crisp; AT&amp;T; SMTP; Pega; Microsoft Office 365; Forge; Avaya; TIBCO; Nessus; AWS Single Sign-On; NuGet; Google Ads; Apache JMeter; ACTIVE Network; Alteryx; Orchard; Cognos; Transformers; Sybase; Onboard Partners; Appium; Track-It!; Okta; VMware vCloud; AWS Multi-Factor Authentication; Built In; Vertex; Shortlist; Microsoft Customer Experience Management; AEM; Microsoft Project Portfolio Management; RMS; x.ai; Microsoft Compliance Manager; Mule ESB; Talent Insights; Resonate; SAP Credit Management; bancassurance; Microsoft Visual Studio; Open Systems; Accenture; OpenVPN; Talent Analytics; AWS Shell; n8n; Google Authenticator; Dialogflow; Google Dialogflow; Zerto; Heatmap; ArcGIS; InTouch; OutSystems; Zycus; Log4j; Teradata; Invoice.to; Salesforce Marketing Cloud; Identity Services; Campaign Manager; Marketing.AI; MuleSoft Anypoint; Mana; Terraform; Docker; Tableau; PostgreSQL; MySQL; Google Cloud Platform; Bitbucket; Kafka; JSON; Golang; Tower; XML; Bamboo; GitHub; Perl; Juniper; Azure Databricks; Databricks; Apache Hadoop; Hadoop; Microsoft TypeScript; Ruby; jQuery; Mac OS; Redux; GitLab; iOS; Gradle; ES6; Cisco ACI; Devise; Scala; Microsoft Windows Server; CSS 3; gRPC; PHP; AWS Lambda; Ability LMS; Apache Cassandra; Cassandra; Amazon DynamoDB; OAuth2; Amazon SQS; Apache Isis; Amazon SNS; JUnit; HTML5; LDAP; Java 8; Azure Monitor; YAML; Groovy; Django; LangGraph; Swift; Kibana; Ubuntu; Coupa; C++; Kotlin; macOS; ML Flow; MLflow; GitHub Actions; Spring Framework; Nagios; GraphQL; Amazon Linux; AWS SDKs; Microsoft Power Automate; Serverless; AppDynamics; Fortify; Elastic APM; Netcracker; Amazon SageMaker; CentOS; MariaDB; Mitre; PySpark; New Relic; Drupal; Microsoft Intune; Rails; Azure DevOps; Kubeflow; AlgoSec; Webex; Proxmox; Apache Tomcat; Argo CD; Meta Llama; Bridge; llama; OpenTelemetry; Citrix XenApp; Logstash; PyTorch; orchestrator; Docker Swarm; HP-UX; Oracle Linux; SUSE; Palo Alto Networks; Forescout; GraphRAG; Bedrock; Windows 10; Microsoft Windows OS; Graylog; ChatGPT; Postman; FinancialForce; Debian; OpenSearch; AWS CloudFormation; Sketch; NVIDIA GPU; Cisco SD-WAN; NetApp; AWS IAM; Azure Storage; Microsoft IIS; Bitbucket Pipelines; Datadog; CyberArk; Pandas; Solarwinds; Adobe Photoshop; VMware ESXi; CUDA; PMD; TalentLMS; Apache Zookeeper; D3.js; Apache iota; Microsoft Graph; VMware vCloud Director; Adobe InDesign; Adobe Illustrator; Snowflake; Drift; Eclipse; Coder; Zoom; Veritas NetBackup; Apache Storm; Gatsby; Mockito; Azure Stack HCI; VMware vSphere; Scale.ai; Azure Arc; Infoblox; Microsoft Fabric; Microsoft Azure Storage; Object Storage; Mule; Curated; Trend Micro; Red Hat Satellite; OData; GitHub Copilot; Amazon Connect; Google Cloud Monitoring; Microsoft OneDrive; OneDrive; LlamaIndex; Workday; Commvault; Azure Application Insights; Eloqua; Visual Studio; Genesys; Microsoft BitLocker; Veeam; NICE CXone; Concur; Azure Cost Management; Tradeshift; SAP Business Suite; Litmus; Automate Ads; Singular; WebMethods; EcoVadis; Rapid Recovery; WORK[etc]; Adobe Experience Cloud; Acra; Saviynt; Salesforce CPQ; Kryon; Archicad; AppsFlyer; Early Warning; MobileIron; SketchUp; BitSight; Optimal Workshop; Secure Suite; SAP GRC; Amazon Athena; Microsoft ATP; Serraview; Event Hub; Sustainalytics; RootCause; Medallia; vuex; Adobe Campaign; Contentsquare; Fortify WebInspect; Microsoft Defender for Identity; Blockchain; AWS Backup; Apprise; Seamless.AI; Sedex; Splitter; Unified streaming; Microsoft PlayReady; Amazon Payment Services; Dayforce; Ekahau; Healthchecks; Localize; Kantar; Braze; NIS; Google Cloud Marketplace; 4D; MSCI; Lucene; Shopify; SAP Financial Accounting; ARCHIBUS; Bitmovin; Achievers; Trifacta; Segment; WorkBook; evolving SEO; WhatsApp; Two Hat; Xperience; Avaya Aura; Google Doubleclick; EY; Amobee; Amazon EMR; Mixpanel; Intelligent Demand; Retargeting; MEGA; Pulsar; Skills Base; Apache Lucene; Abstract; Amazon Web Hosting; Mou; Portfolio Optimization; Objective-C; Rust; Canva; OAuth; Microsoft Azure Active Directory; Podman; Amazon ECS; HBase; Rows; API Platform; Think-Cell; Amazon EKS; Zscaler; VBScript; AWS Identity and Access Management (IAM); SAS; Zookeeper; Microsoft NuGet; GitLab CI; Consul; RabbitMQ; Oracle CRM; Interactive; etcd; Spring Batch; Rocky Linux; Adobe XD; Qlik; IBM Watson; Hortonworks; AWS for SAP</t>
+          <t>Python; Microsoft Excel; Jira; React; Power BI; Provide Support; Docker; Apache Hadoop; Hadoop; Streamline; TypeScript; Microsoft Forefront; Confluence; Redis; Figma; Zoom; Apache Spark; Elastic; ChatGPT; Claude by Anthropic; Microsoft Powerpoint; Kafka; iOS; Thrive; Postman; PyTorch; n8n; GitHub Copilot; Materialize; Workspace; GitHub; Qlik Sense; Google Workspace; NGINX; Webpack; Configure.IT; Testrail; Weex; Next.js; Flutter; Babel; Tailwind; react-testing-library; Monte Carlo; Alteryx; Storybook; Chakra UI; Java; JavaScript; Golang; Mac OS; macOS; Windows Server; Microsoft TypeScript; Microsoft Windows Server; MySQL; Scala; Tableau; C++; Kubernetes; Trello; Microsoft Active Directory; Flask; FastAPI; Active Directory; Node.js; PySpark; eLearning LMS; ServiceNow.com; Cypress; Qlik; Jenkins; CrowdStrike; LiveStream; Scale.ai; Selenium; GitLab; Playwright; Charles; TensorFlow; Freshservice; Jira Service Desk; CrowdStrike Falcon; Oracle; pytest; REST Client; Microsoft Graph; GuardRails; Kibana; Beats; Vite; Zustand; Google Cloud Platform; Cursor; Amazon Web Services; MUI; Gmail; Amazon Cloud Directory; Airflow; Datahub; Prettier; SBT; LangChain; Zoom Phone; Redux; ESLint; Veeam; LangGraph; Rollout; Built In; GraphQL; Elasticsearch; Splunk; Apache Airflow; Google Chrome; User Interviews; Zoom Rooms; Processing; XML; JSON; Falcon; Grafana; Ansible; CSS 3; Hugging Face; TalentLMS; Swift; Objective-C; Kotlin; HTML5; Metabase; Bridge; OAuth; Vue.js; Jest; FreshDesk; Triton; Prometheus; Docker Swarm; KNIME; CUDA; GitLab CI; GitHub Actions; Turning; PostgreSQL; RabbitMQ; CentOS; Ubuntu; JUnit; TestNG</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Fortinet; Windows Server; F5; React Native; AWS Mobile Services; Cisco Routers; Cisco Jasper; Google Ads; Appium; VMware vCloud; Juniper; Mac OS; iOS; Cisco ACI; Microsoft Windows Server; Ubuntu; macOS; Nagios; Amazon Linux; Fortify; CentOS; Microsoft Intune; HP-UX; Oracle Linux; Palo Alto Networks; Windows 10; Microsoft Windows OS; Debian; Cisco SD-WAN; CyberArk; VMware ESXi; VMware vCloud Director; VMware vSphere; Trend Micro; Singular; MobileIron; Mixpanel; Zscaler; Rocky Linux</t>
+          <t>iOS; Flutter; Mac OS; macOS; Windows Server; Microsoft Windows Server; CrowdStrike; CentOS; Ubuntu</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Microsoft Azure; Amazon Web Services; Microsoft Powerpoint; Microsoft Excel; Confluence; Spring; Workspace; Figma; Airflow; Nutanix; Apache Airflow; Amazon CloudWatch; Amazon S3; Cucumber; Microsoft Teams; NVIDIA; Amdocs; SAP SuccessFactors; Microsoft Project; Successfactors; Microsoft SharePoint; Launchpad; Miro; HashiCorp; Microsoft Office 365; Avaya; TIBCO; Microsoft Project Portfolio Management; RMS; InTouch; Marketing.AI; Mana; Google Cloud Platform; Bitbucket; gRPC; PHP; Microsoft Power Automate; Netcracker; Webex; HP-UX; AWS CloudFormation; Sketch; NVIDIA GPU; Azure Storage; Bitbucket Pipelines; Adobe Photoshop; VMware vCloud Director; Adobe InDesign; Adobe Illustrator; Zoom; Infoblox; Microsoft Azure Storage; Object Storage; Red Hat Satellite; Microsoft OneDrive; OneDrive; LlamaIndex; SAP Business Suite; EcoVadis; Archicad; SketchUp; Microsoft Defender for Identity; Sedex; Lucene; ARCHIBUS; Avaya Aura; Amazon EMR; Retargeting; Apache Lucene; Mou; Canva; Rows; Think-Cell; Adobe XD</t>
+          <t>Microsoft Excel; Confluence; Figma; Zoom; Microsoft Powerpoint; Workspace; Google Workspace; Weex; Storybook; Trello; LiveStream; Google Cloud Platform; Amazon Web Services; Airflow; Zoom Phone; Apache Airflow; Zoom Rooms</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Python: last_seen=2026-06-19, first_seen=2022-06-21, confidence=high, jobs=650 | Microsoft Azure: last_seen=2026-06-19, first_seen=2022-06-06, confidence=high, jobs=569 | Amazon Web Services: last_seen=2026-06-15, first_seen=2022-06-06, confidence=high, jobs=530 | Java: last_seen=2026-06-19, first_seen=2022-06-03, confidence=high, jobs=528 | Microsoft Powerpoint: last_seen=2026-06-16, first_seen=2022-03-16, confidence=high, jobs=494 | Microsoft Excel: last_seen=2026-06-16, first_seen=2022-03-16, confidence=high, jobs=411 | SAP: last_seen=2026-06-16, first_seen=2022-03-16, confidence=high, jobs=370 | Jira: last_seen=2026-06-15, first_seen=2022-06-03, confidence=high, jobs=311 | Kubernetes: last_seen=2026-06-19, first_seen=2022-09-27, confidence=high, jobs=305 | Ansible: last_seen=2026-06-19, first_seen=2022-06-21, confidence=high, jobs=270 | Power BI: last_seen=2026-06-19, first_seen=2022-06-09, confidence=high, jobs=255 | Oracle: last_seen=2026-06-19, first_seen=2022-06-03, confidence=high, jobs=235 | JavaScript: last_seen=2026-06-09, first_seen=2022-06-21, confidence=high, jobs=230 | Spring Boot: last_seen=2026-06-15, first_seen=2022-09-22, confidence=high, jobs=220 | Confluence: last_seen=2026-06-10, first_seen=2022-06-07, confidence=high, jobs=197 | Provide Support: last_seen=2026-06-19, first_seen=2022-03-16, confidence=high, jobs=190 | Spring: last_seen=2026-06-15, first_seen=2022-06-07, confidence=high, jobs=188 | Jenkins: last_seen=2026-06-19, first_seen=2022-06-03, confidence=high, jobs=183 | Streamline: last_seen=2026-06-19, first_seen=2022-09-30, confidence=high, jobs=180 | ServiceNow.com: last_seen=2026-06-19, first_seen=2022-07-04, confidence=high, jobs=167 | AWS IoT: last_seen=2026-06-19, first_seen=2022-06-17, confidence=high, jobs=165 | Microsoft Forefront: last_seen=2026-06-19, first_seen=2024-02-05, confidence=high, jobs=157 | Node.js: last_seen=2026-06-19, first_seen=2022-09-19, confidence=high, jobs=149 | MongoDB: last_seen=2026-06-15, first_seen=2022-09-29, confidence=high, jobs=132 | Red Hat: last_seen=2026-06-19, first_seen=2022-09-27, confidence=high, jobs=130 | AWS Managed Services: last_seen=2026-06-15, first_seen=2022-06-21, confidence=high, jobs=129 | React: last_seen=2026-06-07, first_seen=2022-10-14, confidence=high, jobs=119 | PowerShell: last_seen=2026-06-19, first_seen=2022-09-26, confidence=high, jobs=116 | ELK: last_seen=2026-06-19, first_seen=2022-09-27, confidence=high, jobs=111 | Microsoft Active Directory: last_seen=2026-06-19, first_seen=2022-09-29, confidence=high, jobs=108 | Apache Maven: last_seen=2025-07-17, first_seen=2022-06-07, confidence=high, jobs=104 | Active Directory: last_seen=2026-06-19, first_seen=2022-12-15, confidence=high, jobs=103 | Fortinet: last_seen=2026-06-14, first_seen=2023-01-19, confidence=high, jobs=102 | OpenStack: last_seen=2026-06-15, first_seen=2022-09-28, confidence=high, jobs=99 | Apache Spark: last_seen=2026-06-19, first_seen=2022-06-24, confidence=high, jobs=98 | Salesforce: last_seen=2026-06-16, first_seen=2022-06-20, confidence=high, jobs=92 | Grafana: last_seen=2026-06-19, first_seen=2022-10-17, confidence=high, jobs=91 | Root Cause: last_seen=2026-06-14, first_seen=2022-10-19, confidence=high, jobs=90 | Yarn: last_seen=2025-05-12, first_seen=2023-03-15, confidence=high, jobs=85 | Prometheus: last_seen=2026-06-19, first_seen=2022-10-17, confidence=high, jobs=80 | Elasticsearch: last_seen=2026-06-01, first_seen=2022-11-07, confidence=high, jobs=79 | Redis: last_seen=2025-07-17, first_seen=2022-09-28, confidence=high, jobs=76 | SonarQube: last_seen=2026-06-15, first_seen=2022-11-10, confidence=high, jobs=76 | NGINX: last_seen=2026-06-09, first_seen=2022-11-03, confidence=high, jobs=75 | J2EE: last_seen=2026-04-10, first_seen=2022-06-07, confidence=high, jobs=74 | Network Solutions: last_seen=2026-06-14, first_seen=2022-03-16, confidence=high, jobs=73 | MSSQL: last_seen=2026-05-30, first_seen=2022-09-27, confidence=high, jobs=73 | Windows Server: last_seen=2026-04-02, first_seen=2022-10-18, confidence=high, jobs=68 | TypeScript: last_seen=2026-06-11, first_seen=2022-10-25, confidence=high, jobs=68 | SAP Ariba: last_seen=2026-06-14, first_seen=2022-06-14, confidence=high, jobs=67 | Dynatrace: last_seen=2026-06-03, first_seen=2022-11-03, confidence=high, jobs=67 | Microsoft Hyper-V: last_seen=2026-06-19, first_seen=2022-09-29, confidence=high, jobs=59 | Google Surveys: last_seen=2026-06-12, first_seen=2023-01-05, confidence=high, jobs=57 | Workspace: last_seen=2026-06-08, first_seen=2022-06-14, confidence=high, jobs=55 | Apigee: last_seen=2025-12-17, first_seen=2022-09-27, confidence=high, jobs=53 | Webpack: last_seen=2025-07-17, first_seen=2022-10-25, confidence=high, jobs=53 | eLearning LMS: last_seen=2026-06-06, first_seen=2022-10-19, confidence=high, jobs=52 | JBoss: last_seen=2026-04-10, first_seen=2022-06-07, confidence=high, jobs=48 | GuardRails: last_seen=2026-06-19, first_seen=2023-06-06, confidence=high, jobs=46 | Figma: last_seen=2026-06-04, first_seen=2023-03-01, confidence=high, jobs=46 | Apache Camel: last_seen=2026-06-15, first_seen=2022-10-17, confidence=high, jobs=46 | Airflow: last_seen=2026-05-25, first_seen=2022-10-07, confidence=high, jobs=46 | Nutanix: last_seen=2026-06-19, first_seen=2022-10-05, confidence=high, jobs=46 | Apache Airflow: last_seen=2026-05-25, first_seen=2022-10-07, confidence=high, jobs=46 | Processing: last_seen=2026-06-12, first_seen=2023-05-10, confidence=high, jobs=45 | Amazon CloudWatch: last_seen=2026-06-03, first_seen=2022-11-03, confidence=high, jobs=44 | AWS Auto Scaling: last_seen=2026-03-05, first_seen=2022-11-04, confidence=high, jobs=44 | Superhuman: last_seen=2025-05-05, first_seen=2023-11-08, confidence=high, jobs=44 | Amazon S3: last_seen=2026-06-05, first_seen=2022-09-28, confidence=high, jobs=44 | Macro: last_seen=2026-05-06, first_seen=2022-06-30, confidence=high, jobs=43 | Silver Peak: last_seen=2026-05-14, first_seen=2022-10-06, confidence=high, jobs=43 | KVM: last_seen=2026-06-14, first_seen=2022-12-15, confidence=high, jobs=42 | Microsoft Visio: last_seen=2026-06-16, first_seen=2022-09-19, confidence=high, jobs=42 | Bootstrap: last_seen=2025-07-17, first_seen=2022-12-16, confidence=high, jobs=42 | F5: last_seen=2026-05-26, first_seen=2022-06-20, confidence=high, jobs=42 | Amazon RDS: last_seen=2026-06-05, first_seen=2022-09-28, confidence=high, jobs=41 | LangChain: last_seen=2026-06-07, first_seen=2024-07-29, confidence=high, jobs=40 | Cucumber: last_seen=2025-12-06, first_seen=2022-06-03, confidence=high, jobs=40 | Azure Stack: last_seen=2026-06-15, first_seen=2022-10-07, confidence=high, jobs=39 | VeloCloud: last_seen=2026-05-14, first_seen=2022-10-06, confidence=high, jobs=38 | JSON API: last_seen=2025-08-21, first_seen=2022-09-28, confidence=high, jobs=37 | Zabbix: last_seen=2026-06-15, first_seen=2023-02-06, confidence=high, jobs=37 | Selenium: last_seen=2025-12-06, first_seen=2022-06-03, confidence=high, jobs=37 | C#: last_seen=2026-05-04, first_seen=2022-09-29, confidence=high, jobs=36 | Google Analytics: last_seen=2026-06-04, first_seen=2022-06-06, confidence=high, jobs=36 | Splunk: last_seen=2026-05-28, first_seen=2022-06-30, confidence=high, jobs=35 | Sanity: last_seen=2026-05-28, first_seen=2023-01-11, confidence=high, jobs=34 | Soap UI: last_seen=2026-06-15, first_seen=2022-11-23, confidence=high, jobs=34 | Ivalua: last_seen=2026-06-04, first_seen=2025-01-20, confidence=high, jobs=34 | Microsoft Teams: last_seen=2026-06-12, first_seen=2022-09-29, confidence=high, jobs=33 | TensorFlow: last_seen=2026-06-10, first_seen=2022-12-16, confidence=high, jobs=33 | Helm: last_seen=2026-05-28, first_seen=2023-02-06, confidence=high, jobs=33 | Microsoft Power Apps: last_seen=2026-06-17, first_seen=2022-10-27, confidence=high, jobs=33 | SAP S/4HANA (SAP Cloud ERP): last_seen=2026-06-12, first_seen=2023-05-11, confidence=high, jobs=31 | NVIDIA: last_seen=2026-06-14, first_seen=2025-03-07, confidence=high, jobs=31 | Amdocs: last_seen=2026-06-13, first_seen=2023-01-03, confidence=high, jobs=31 | Kong: last_seen=2025-12-17, first_seen=2022-11-03, confidence=high, jobs=29 | Elastic: last_seen=2026-06-01, first_seen=2022-06-30, confidence=high, jobs=28 | Benchmark: last_seen=2026-06-10, first_seen=2022-10-19, confidence=high, jobs=27 | Microsoft Power Platform: last_seen=2026-06-17, first_seen=2023-02-10, confidence=high, jobs=27 | AWS Data Exchange: last_seen=2026-06-04, first_seen=2022-10-05, confidence=high, jobs=27 | React Native: last_seen=2026-05-04, first_seen=2022-10-14, confidence=high, jobs=26 | CRD: last_seen=2026-06-05, first_seen=2022-09-19, confidence=high, jobs=26 | AWS Command Line Interface: last_seen=2026-02-16, first_seen=2023-02-06, confidence=high, jobs=25 | SAP SuccessFactors: last_seen=2026-05-10, first_seen=2022-11-16, confidence=high, jobs=24 | Istio: last_seen=2025-10-18, first_seen=2022-11-03, confidence=high, jobs=24 | Adobe Experience Manager: last_seen=2026-06-01, first_seen=2022-11-18, confidence=high, jobs=24 | Microsoft Project: last_seen=2026-06-11, first_seen=2022-09-19, confidence=high, jobs=24 | Successfactors: last_seen=2026-05-10, first_seen=2022-11-16, confidence=high, jobs=24 | Google VPC: last_seen=2026-04-01, first_seen=2022-12-24, confidence=high, jobs=24 | Microsoft SharePoint: last_seen=2026-05-11, first_seen=2022-12-07, confidence=high, jobs=23 | Review Board: last_seen=2026-06-12, first_seen=2022-10-18, confidence=high, jobs=23 | Envoy: last_seen=2025-10-18, first_seen=2022-11-03, confidence=high, jobs=22 | SailPoint: last_seen=2026-06-19, first_seen=2023-06-13, confidence=high, jobs=22 | AWS Mobile Services: last_seen=2026-05-11, first_seen=2022-09-28, confidence=high, jobs=21 | Microsoft Outlook: last_seen=2026-05-12, first_seen=2025-02-06, confidence=high, jobs=21 | Runbook: last_seen=2026-06-19, first_seen=2023-08-14, confidence=high, jobs=21 | SAP FICO: last_seen=2026-06-11, first_seen=2022-10-25, confidence=high, jobs=21 | Radware: last_seen=2026-05-26, first_seen=2023-01-19, confidence=high, jobs=20 | Control-M: last_seen=2026-06-08, first_seen=2022-06-30, confidence=high, jobs=19 | Azure Active Directory: last_seen=2026-01-02, first_seen=2023-06-13, confidence=high, jobs=19 | Vault: last_seen=2026-05-23, first_seen=2023-02-06, confidence=high, jobs=19 | Catalyst: last_seen=2026-05-26, first_seen=2023-02-13, confidence=high, jobs=19 | Red Hat OpenShift: last_seen=2026-06-19, first_seen=2024-12-20, confidence=high, jobs=19 | Tagetik: last_seen=2026-06-15, first_seen=2025-01-02, confidence=high, jobs=18 | Symantec: last_seen=2026-05-20, first_seen=2024-06-27, confidence=high, jobs=18 | Viptela: last_seen=2026-06-04, first_seen=2024-05-28, confidence=high, jobs=18 | Xpand: last_seen=2023-03-22, first_seen=2023-02-14, confidence=high, jobs=17 | Oracle Database: last_seen=2026-02-24, first_seen=2023-01-30, confidence=high, jobs=17 | Cisco Routers: last_seen=2026-05-26, first_seen=2022-07-04, confidence=high, jobs=16 | Launchpad: last_seen=2026-01-19, first_seen=2024-12-03, confidence=high, jobs=15 | Attribution: last_seen=2026-06-09, first_seen=2022-10-05, confidence=high, jobs=15 | Sharpen: last_seen=2026-05-11, first_seen=2023-01-03, confidence=high, jobs=15 | Intel: last_seen=2026-06-08, first_seen=2022-11-16, confidence=high, jobs=14 | Sungard: last_seen=2026-06-11, first_seen=2022-10-25, confidence=high, jobs=14 | Delta Lake: last_seen=2026-06-07, first_seen=2023-03-15, confidence=high, jobs=14 | Microsoft Exchange Online: last_seen=2025-07-02, first_seen=2022-07-03, confidence=high, jobs=13 | Argo: last_seen=2023-11-10, first_seen=2022-11-03, confidence=high, jobs=13 | Miro: last_seen=2026-03-13, first_seen=2022-12-12, confidence=high, jobs=13 | Crossplane: last_seen=2023-11-10, first_seen=2022-11-03, confidence=high, jobs=13 | HashiCorp: last_seen=2026-01-02, first_seen=2022-12-30, confidence=high, jobs=12 | Cisco Jasper: last_seen=2026-06-05, first_seen=2022-11-19, confidence=high, jobs=12 | Crisp: last_seen=2026-06-19, first_seen=2023-03-14, confidence=high, jobs=12 | AT&amp;T: last_seen=2026-06-04, first_seen=2023-06-21, confidence=high, jobs=11 | SMTP: last_seen=2026-02-04, first_seen=2023-02-09, confidence=high, jobs=11 | Pega: last_seen=2025-05-12, first_seen=2022-06-30, confidence=high, jobs=11 | Microsoft Office 365: last_seen=2026-05-28, first_seen=2023-06-19, confidence=high, jobs=11 | Forge: last_seen=2026-06-11, first_seen=2024-07-29, confidence=high, jobs=11 | Avaya: last_seen=2024-11-14, first_seen=2023-05-15, confidence=high, jobs=10 | TIBCO: last_seen=2026-04-10, first_seen=2023-01-17, confidence=high, jobs=10 | Nessus: last_seen=2026-01-31, first_seen=2023-02-07, confidence=high, jobs=10 | AWS Single Sign-On: last_seen=2023-11-06, first_seen=2023-05-18, confidence=high, jobs=10 | NuGet: last_seen=2025-11-14, first_seen=2022-11-17, confidence=high, jobs=9 | Google Ads: last_seen=2026-06-01, first_seen=2022-06-06, confidence=high, jobs=9 | Apache JMeter: last_seen=2025-12-06, first_seen=2023-03-21, confidence=high, jobs=9 | ACTIVE Network: last_seen=2026-04-26, first_seen=2022-09-19, confidence=high, jobs=9 | Alteryx: last_seen=2025-06-20, first_seen=2022-06-09, confidence=high, jobs=9 | Orchard: last_seen=2023-05-24, first_seen=2022-10-18, confidence=high, jobs=9 | Cognos: last_seen=2025-06-20, first_seen=2022-06-15, confidence=high, jobs=9 | Transformers: last_seen=2026-03-25, first_seen=2023-01-17, confidence=high, jobs=9 | Sybase: last_seen=2024-08-01, first_seen=2022-09-26, confidence=high, jobs=9 | Onboard Partners: last_seen=2026-06-04, first_seen=2024-07-15, confidence=high, jobs=9 | Appium: last_seen=2024-07-01, first_seen=2023-03-21, confidence=high, jobs=8 | Track-It!: last_seen=2026-04-26, first_seen=2022-09-19, confidence=high, jobs=8 | Track-It!: last_seen=2026-04-26, first_seen=2022-09-19, confidence=high, jobs=8 | Okta: last_seen=2026-05-19, first_seen=2023-06-13, confidence=high, jobs=8 | VMware vCloud: last_seen=2026-01-02, first_seen=2022-11-19, confidence=high, jobs=8 | AWS Multi-Factor Authentication: last_seen=2026-01-29, first_seen=2023-06-13, confidence=high, jobs=8 | Built In: last_seen=2026-06-07, first_seen=2023-05-29, confidence=high, jobs=8 | Vertex: last_seen=2026-05-13, first_seen=2025-07-09, confidence=high, jobs=8 | Shortlist: last_seen=2025-09-09, first_seen=2023-03-14, confidence=high, jobs=7 | Microsoft Customer Experience Management: last_seen=2026-06-11, first_seen=2023-05-25, confidence=high, jobs=7 | AEM: last_seen=2025-05-15, first_seen=2022-06-16, confidence=high, jobs=7 | Microsoft Project Portfolio Management: last_seen=2024-07-31, first_seen=2023-01-18, confidence=high, jobs=7 | RMS: last_seen=2024-08-12, first_seen=2022-07-08, confidence=high, jobs=7 | x.ai: last_seen=2026-05-13, first_seen=2025-11-16, confidence=high, jobs=6 | Microsoft Compliance Manager: last_seen=2024-04-02, first_seen=2022-10-18, confidence=high, jobs=6 | Mule ESB: last_seen=2026-05-21, first_seen=2022-09-30, confidence=high, jobs=6 | Talent Insights: last_seen=2026-05-28, first_seen=2024-01-31, confidence=high, jobs=6 | Resonate: last_seen=2024-12-19, first_seen=2022-06-24, confidence=high, jobs=5 | SAP Credit Management: last_seen=2026-06-11, first_seen=2026-02-10, confidence=high, jobs=5 | bancassurance: last_seen=2025-12-28, first_seen=2022-10-28, confidence=high, jobs=5 | Microsoft Visual Studio: last_seen=2025-11-14, first_seen=2022-10-17, confidence=high, jobs=5 | Open Systems: last_seen=2023-08-09, first_seen=2023-01-30, confidence=high, jobs=5 | Accenture: last_seen=2024-10-14, first_seen=2023-09-13, confidence=high, jobs=5 | OpenVPN: last_seen=2025-12-17, first_seen=2024-03-12, confidence=high, jobs=5 | Talent Analytics: last_seen=2025-11-29, first_seen=2023-06-05, confidence=high, jobs=5 | AWS Shell: last_seen=2023-09-11, first_seen=2023-02-06, confidence=high, jobs=5 | n8n: last_seen=2026-05-22, first_seen=2025-12-08, confidence=high, jobs=5 | Google Authenticator: last_seen=2023-11-06, first_seen=2023-06-13, confidence=high, jobs=5 | Dialogflow: last_seen=2026-05-09, first_seen=2025-02-26, confidence=high, jobs=4 | Google Dialogflow: last_seen=2026-05-09, first_seen=2025-02-26, confidence=high, jobs=4 | Zerto: last_seen=2023-05-13, first_seen=2022-10-05, confidence=high, jobs=4 | Heatmap: last_seen=2026-03-23, first_seen=2025-06-19, confidence=high, jobs=4 | ArcGIS: last_seen=2026-04-02, first_seen=2025-11-03, confidence=high, jobs=4 | InTouch: last_seen=2023-12-04, first_seen=2022-11-10, confidence=high, jobs=4 | OutSystems: last_seen=2025-07-10, first_seen=2025-02-25, confidence=high, jobs=4 | Zycus: last_seen=2025-05-28, first_seen=2022-10-19, confidence=high, jobs=4 | Log4j: last_seen=2023-08-07, first_seen=2023-07-07, confidence=high, jobs=4 | Teradata: last_seen=2025-06-20, first_seen=2022-06-14, confidence=high, jobs=4 | Invoice.to: last_seen=2026-02-04, first_seen=2025-12-12, confidence=high, jobs=3 | Salesforce Marketing Cloud: last_seen=2025-05-12, first_seen=2022-07-11, confidence=high, jobs=3 | Identity Services: last_seen=2023-11-06, first_seen=2023-06-13, confidence=high, jobs=3 | Campaign Manager: last_seen=2024-08-20, first_seen=2024-08-08, confidence=high, jobs=2 | Marketing.AI: last_seen=2026-05-25, first_seen=2026-05-25, confidence=high, jobs=1 | MuleSoft Anypoint: last_seen=2026-05-21, first_seen=2026-01-12, confidence=high, jobs=1 | Mana: last_seen=2022-07-11, first_seen=2022-07-11, confidence=high, jobs=1 | Terraform: last_seen=2026-06-19, first_seen=2022-10-07, confidence=medium, jobs=207 | Docker: last_seen=2026-06-15, first_seen=2022-09-28, confidence=medium, jobs=197 | Tableau: last_seen=2026-06-19, first_seen=2022-06-04, confidence=medium, jobs=196 | PostgreSQL: last_seen=2026-06-19, first_seen=2022-06-07, confidence=medium, jobs=191 | MySQL: last_seen=2026-06-19, first_seen=2022-06-07, confidence=medium, jobs=191 | Google Cloud Platform: last_seen=2026-06-14, first_seen=2022-06-24, confidence=medium, jobs=190 | Bitbucket: last_seen=2026-06-14, first_seen=2022-06-24, confidence=medium, jobs=157 | Kafka: last_seen=2026-06-11, first_seen=2022-06-30, confidence=medium, jobs=138 | JSON: last_seen=2026-06-19, first_seen=2022-07-01, confidence=medium, jobs=129 | Golang: last_seen=2026-06-11, first_seen=2022-11-03, confidence=medium, jobs=117 | Tower: last_seen=2026-03-11, first_seen=2022-06-15, confidence=medium, jobs=100 | XML: last_seen=2026-06-19, first_seen=2022-06-07, confidence=medium, jobs=95 | Bamboo: last_seen=2026-06-10, first_seen=2022-11-09, confidence=medium, jobs=92 | GitHub: last_seen=2026-06-14, first_seen=2022-06-24, confidence=medium, jobs=90 | Perl: last_seen=2026-05-03, first_seen=2022-11-07, confidence=medium, jobs=88 | Juniper: last_seen=2026-06-14, first_seen=2022-11-10, confidence=medium, jobs=81 | Azure Databricks: last_seen=2026-06-09, first_seen=2022-07-01, confidence=medium, jobs=74 | Databricks: last_seen=2026-06-09, first_seen=2022-07-01, confidence=medium, jobs=74 | Apache Hadoop: last_seen=2026-05-25, first_seen=2022-09-28, confidence=medium, jobs=74 | Hadoop: last_seen=2026-05-25, first_seen=2022-09-28, confidence=medium, jobs=74 | Microsoft TypeScript: last_seen=2026-06-11, first_seen=2022-10-25, confidence=medium, jobs=68 | Ruby: last_seen=2026-05-14, first_seen=2022-06-03, confidence=medium, jobs=63 | jQuery: last_seen=2025-07-17, first_seen=2022-11-23, confidence=medium, jobs=60 | Mac OS: last_seen=2026-05-08, first_seen=2023-02-09, confidence=medium, jobs=59 | Redux: last_seen=2026-04-07, first_seen=2022-10-25, confidence=medium, jobs=57 | GitLab: last_seen=2026-05-28, first_seen=2022-12-30, confidence=medium, jobs=56 | iOS: last_seen=2026-05-21, first_seen=2022-10-14, confidence=medium, jobs=56 | Gradle: last_seen=2025-08-21, first_seen=2022-11-10, confidence=medium, jobs=53 | ES6: last_seen=2025-07-17, first_seen=2022-10-25, confidence=medium, jobs=51 | Cisco ACI: last_seen=2026-05-26, first_seen=2022-06-21, confidence=medium, jobs=50 | Devise: last_seen=2026-05-25, first_seen=2022-10-12, confidence=medium, jobs=50 | Scala: last_seen=2026-05-17, first_seen=2022-06-24, confidence=medium, jobs=48 | Microsoft Windows Server: last_seen=2026-04-02, first_seen=2022-10-18, confidence=medium, jobs=48 | CSS 3: last_seen=2026-02-06, first_seen=2022-10-25, confidence=medium, jobs=47 | gRPC: last_seen=2026-05-14, first_seen=2022-09-22, confidence=medium, jobs=47 | PHP: last_seen=2026-03-26, first_seen=2022-06-21, confidence=medium, jobs=45 | AWS Lambda: last_seen=2026-06-05, first_seen=2022-09-28, confidence=medium, jobs=45 | Ability LMS: last_seen=2026-06-11, first_seen=2022-06-27, confidence=medium, jobs=44 | Apache Cassandra: last_seen=2025-07-17, first_seen=2022-12-16, confidence=medium, jobs=40 | Cassandra: last_seen=2025-07-17, first_seen=2022-12-16, confidence=medium, jobs=40 | Amazon DynamoDB: last_seen=2025-08-21, first_seen=2022-09-28, confidence=medium, jobs=39 | OAuth2: last_seen=2026-05-14, first_seen=2022-09-22, confidence=medium, jobs=38 | Amazon SQS: last_seen=2025-08-21, first_seen=2022-09-28, confidence=medium, jobs=38 | Apache Isis: last_seen=2026-06-11, first_seen=2023-02-21, confidence=medium, jobs=37 | Amazon SNS: last_seen=2025-08-21, first_seen=2022-09-28, confidence=medium, jobs=37 | JUnit: last_seen=2024-03-25, first_seen=2022-09-28, confidence=medium, jobs=37 | HTML5: last_seen=2026-04-24, first_seen=2022-06-30, confidence=medium, jobs=36 | LDAP: last_seen=2026-06-19, first_seen=2023-02-09, confidence=medium, jobs=36 | Java 8: last_seen=2024-03-25, first_seen=2022-09-28, confidence=medium, jobs=35 | Azure Monitor: last_seen=2026-06-10, first_seen=2023-02-06, confidence=medium, jobs=34 | YAML: last_seen=2026-06-10, first_seen=2022-10-07, confidence=medium, jobs=34 | Groovy: last_seen=2026-06-04, first_seen=2022-10-18, confidence=medium, jobs=33 | Django: last_seen=2026-06-19, first_seen=2022-11-04, confidence=medium, jobs=32 | LangGraph: last_seen=2026-05-14, first_seen=2025-07-09, confidence=medium, jobs=31 | Swift: last_seen=2024-09-25, first_seen=2022-06-03, confidence=medium, jobs=30 | Kibana: last_seen=2026-06-01, first_seen=2022-12-15, confidence=medium, jobs=30 | Ubuntu: last_seen=2026-06-10, first_seen=2024-04-04, confidence=medium, jobs=29 | Coupa: last_seen=2026-06-14, first_seen=2022-10-19, confidence=medium, jobs=28 | C++: last_seen=2026-04-29, first_seen=2022-10-17, confidence=medium, jobs=28 | Kotlin: last_seen=2025-06-25, first_seen=2022-10-14, confidence=medium, jobs=28 | macOS: last_seen=2025-09-09, first_seen=2023-04-04, confidence=medium, jobs=28 | ML Flow: last_seen=2026-06-08, first_seen=2025-07-09, confidence=medium, jobs=27 | MLflow: last_seen=2026-06-08, first_seen=2025-07-09, confidence=medium, jobs=27 | GitHub Actions: last_seen=2026-06-14, first_seen=2023-02-06, confidence=medium, jobs=26 | Spring Framework: last_seen=2025-06-24, first_seen=2022-10-26, confidence=medium, jobs=25 | Nagios: last_seen=2026-02-16, first_seen=2022-11-07, confidence=medium, jobs=25 | GraphQL: last_seen=2026-05-01, first_seen=2022-11-18, confidence=medium, jobs=25 | Amazon Linux: last_seen=2026-04-24, first_seen=2022-11-03, confidence=medium, jobs=25 | AWS SDKs: last_seen=2026-06-10, first_seen=2023-02-06, confidence=medium, jobs=24 | Microsoft Power Automate: last_seen=2026-06-17, first_seen=2023-09-19, confidence=medium, jobs=24 | Serverless: last_seen=2026-06-03, first_seen=2022-09-28, confidence=medium, jobs=24 | AppDynamics: last_seen=2023-11-10, first_seen=2022-11-03, confidence=medium, jobs=23 | Fortify: last_seen=2025-04-16, first_seen=2022-11-10, confidence=medium, jobs=22 | Elastic APM: last_seen=2023-11-10, first_seen=2022-11-03, confidence=medium, jobs=22 | Netcracker: last_seen=2026-06-01, first_seen=2022-10-18, confidence=medium, jobs=22 | Amazon SageMaker: last_seen=2026-05-13, first_seen=2025-07-09, confidence=medium, jobs=21 | CentOS: last_seen=2026-06-10, first_seen=2022-10-19, confidence=medium, jobs=21 | MariaDB: last_seen=2026-06-15, first_seen=2022-10-17, confidence=medium, jobs=20 | Mitre: last_seen=2026-06-04, first_seen=2023-06-21, confidence=medium, jobs=19 | PySpark: last_seen=2026-06-09, first_seen=2022-06-24, confidence=medium, jobs=19 | New Relic: last_seen=2025-12-17, first_seen=2023-02-06, confidence=medium, jobs=19 | Drupal: last_seen=2024-08-08, first_seen=2022-12-16, confidence=medium, jobs=19 | Microsoft Intune: last_seen=2025-11-01, first_seen=2022-10-18, confidence=medium, jobs=19 | Rails: last_seen=2024-08-08, first_seen=2022-11-04, confidence=medium, jobs=18 | Azure DevOps: last_seen=2026-05-16, first_seen=2023-01-30, confidence=medium, jobs=18 | Kubeflow: last_seen=2026-05-13, first_seen=2025-07-09, confidence=medium, jobs=18 | AlgoSec: last_seen=2026-05-26, first_seen=2023-01-19, confidence=medium, jobs=18 | Webex: last_seen=2026-03-26, first_seen=2023-08-02, confidence=medium, jobs=17 | Proxmox: last_seen=2026-05-27, first_seen=2024-10-08, confidence=medium, jobs=17 | Apache Tomcat: last_seen=2026-05-03, first_seen=2023-07-17, confidence=medium, jobs=17 | Argo CD: last_seen=2026-05-28, first_seen=2022-11-03, confidence=medium, jobs=16 | Meta Llama: last_seen=2026-05-25, first_seen=2024-07-29, confidence=medium, jobs=16 | Bridge: last_seen=2026-02-24, first_seen=2022-11-19, confidence=medium, jobs=16 | llama: last_seen=2026-05-25, first_seen=2024-07-29, confidence=medium, jobs=16 | OpenTelemetry: last_seen=2026-05-01, first_seen=2022-11-03, confidence=medium, jobs=16 | Citrix XenApp: last_seen=2026-04-02, first_seen=2022-12-15, confidence=medium, jobs=16 | Logstash: last_seen=2026-06-01, first_seen=2022-12-15, confidence=medium, jobs=15 | PyTorch: last_seen=2026-06-10, first_seen=2024-07-29, confidence=medium, jobs=15 | orchestrator: last_seen=2025-09-02, first_seen=2022-10-17, confidence=medium, jobs=15 | Docker Swarm: last_seen=2025-12-17, first_seen=2023-02-06, confidence=medium, jobs=15 | HP-UX: last_seen=2026-05-11, first_seen=2022-10-19, confidence=medium, jobs=15 | Oracle Linux: last_seen=2026-05-03, first_seen=2023-07-17, confidence=medium, jobs=15 | SUSE: last_seen=2026-05-03, first_seen=2023-07-17, confidence=medium, jobs=15 | Palo Alto Networks: last_seen=2026-05-30, first_seen=2024-04-04, confidence=medium, jobs=14 | Forescout: last_seen=2026-05-26, first_seen=2024-08-02, confidence=medium, jobs=14 | GraphRAG: last_seen=2026-05-13, first_seen=2025-07-09, confidence=medium, jobs=14 | Bedrock: last_seen=2026-05-13, first_seen=2025-07-09, confidence=medium, jobs=14 | Windows 10: last_seen=2026-05-28, first_seen=2023-01-05, confidence=medium, jobs=14 | Microsoft Windows OS: last_seen=2025-06-05, first_seen=2022-10-18, confidence=medium, jobs=14 | Graylog: last_seen=2025-07-17, first_seen=2024-04-04, confidence=medium, jobs=13 | ChatGPT: last_seen=2026-03-11, first_seen=2024-12-03, confidence=medium, jobs=13 | Postman: last_seen=2025-12-06, first_seen=2022-11-19, confidence=medium, jobs=13 | FinancialForce: last_seen=2026-06-15, first_seen=2025-12-12, confidence=medium, jobs=13 | Debian: last_seen=2025-07-30, first_seen=2022-11-10, confidence=medium, jobs=13 | OpenSearch: last_seen=2025-07-17, first_seen=2024-04-04, confidence=medium, jobs=13 | AWS CloudFormation: last_seen=2025-06-18, first_seen=2023-05-14, confidence=medium, jobs=12 | Sketch: last_seen=2025-08-20, first_seen=2023-03-01, confidence=medium, jobs=12 | NVIDIA GPU: last_seen=2026-06-10, first_seen=2025-12-27, confidence=medium, jobs=12 | Cisco SD-WAN: last_seen=2026-05-14, first_seen=2024-10-08, confidence=medium, jobs=12 | NetApp: last_seen=2026-03-26, first_seen=2023-04-25, confidence=medium, jobs=11 | AWS IAM: last_seen=2026-06-12, first_seen=2025-05-09, confidence=medium, jobs=11 | Azure Storage: last_seen=2026-01-02, first_seen=2022-10-19, confidence=medium, jobs=11 | Microsoft IIS: last_seen=2025-06-05, first_seen=2022-12-15, confidence=medium, jobs=11 | Bitbucket Pipelines: last_seen=2026-06-14, first_seen=2023-03-13, confidence=medium, jobs=10 | Datadog: last_seen=2026-05-01, first_seen=2023-06-26, confidence=medium, jobs=10 | CyberArk: last_seen=2026-06-19, first_seen=2023-02-07, confidence=medium, jobs=10 | Pandas: last_seen=2026-06-10, first_seen=2025-01-22, confidence=medium, jobs=10 | Solarwinds: last_seen=2026-04-25, first_seen=2024-07-24, confidence=medium, jobs=10 | Adobe Photoshop: last_seen=2026-01-28, first_seen=2022-06-16, confidence=medium, jobs=9 | VMware ESXi: last_seen=2026-06-14, first_seen=2026-02-03, confidence=medium, jobs=9 | CUDA: last_seen=2026-06-10, first_seen=2024-09-03, confidence=medium, jobs=9 | PMD: last_seen=2026-05-15, first_seen=2024-01-12, confidence=medium, jobs=9 | TalentLMS: last_seen=2026-01-15, first_seen=2022-10-12, confidence=medium, jobs=9 | Apache Zookeeper: last_seen=2025-10-18, first_seen=2023-02-06, confidence=medium, jobs=9 | D3.js: last_seen=2024-10-16, first_seen=2023-02-06, confidence=medium, jobs=8 | Apache iota: last_seen=2026-06-05, first_seen=2024-04-25, confidence=medium, jobs=8 | Microsoft Graph: last_seen=2026-04-29, first_seen=2022-09-19, confidence=medium, jobs=8 | VMware vCloud Director: last_seen=2026-01-02, first_seen=2022-11-19, confidence=medium, jobs=8 | Adobe InDesign: last_seen=2026-01-28, first_seen=2022-06-16, confidence=medium, jobs=8 | Adobe Illustrator: last_seen=2026-01-28, first_seen=2022-12-14, confidence=medium, jobs=8 | Snowflake: last_seen=2024-11-26, first_seen=2023-03-15, confidence=medium, jobs=8 | Drift: last_seen=2026-06-11, first_seen=2024-07-29, confidence=medium, jobs=8 | Eclipse: last_seen=2025-01-07, first_seen=2022-06-07, confidence=medium, jobs=8 | Coder: last_seen=2023-12-27, first_seen=2022-10-14, confidence=medium, jobs=8 | Zoom: last_seen=2026-01-31, first_seen=2022-09-29, confidence=medium, jobs=8 | Veritas NetBackup: last_seen=2024-08-19, first_seen=2022-10-19, confidence=medium, jobs=8 | Apache Storm: last_seen=2026-06-09, first_seen=2024-02-02, confidence=medium, jobs=8 | Gatsby: last_seen=2023-05-16, first_seen=2022-10-25, confidence=medium, jobs=8 | Mockito: last_seen=2024-03-25, first_seen=2022-11-10, confidence=medium, jobs=8 | Azure Stack HCI: last_seen=2023-01-30, first_seen=2022-10-07, confidence=medium, jobs=7 | VMware vSphere: last_seen=2025-08-19, first_seen=2022-12-15, confidence=medium, jobs=7 | Scale.ai: last_seen=2026-06-08, first_seen=2025-04-29, confidence=medium, jobs=7 | Azure Arc: last_seen=2026-03-13, first_seen=2022-12-30, confidence=medium, jobs=7 | Infoblox: last_seen=2026-06-09, first_seen=2024-07-24, confidence=medium, jobs=7 | Microsoft Fabric: last_seen=2026-06-07, first_seen=2025-07-09, confidence=medium, jobs=7 | Microsoft Azure Storage: last_seen=2025-07-07, first_seen=2022-10-17, confidence=medium, jobs=7 | Object Storage: last_seen=2026-05-28, first_seen=2024-09-03, confidence=medium, jobs=7 | Mule: last_seen=2026-05-21, first_seen=2022-09-30, confidence=medium, jobs=6 | Curated: last_seen=2026-05-10, first_seen=2025-09-03, confidence=medium, jobs=6 | Trend Micro: last_seen=2026-01-31, first_seen=2023-02-06, confidence=medium, jobs=6 | Red Hat Satellite: last_seen=2023-12-20, first_seen=2023-07-17, confidence=medium, jobs=6 | OData: last_seen=2024-04-29, first_seen=2022-11-18, confidence=medium, jobs=6 | GitHub Copilot: last_seen=2026-05-16, first_seen=2025-07-13, confidence=medium, jobs=6 | Amazon Connect: last_seen=2026-01-31, first_seen=2023-01-12, confidence=medium, jobs=6 | Google Cloud Monitoring: last_seen=2024-04-06, first_seen=2023-04-14, confidence=medium, jobs=5 | Microsoft OneDrive: last_seen=2024-05-20, first_seen=2022-07-03, confidence=medium, jobs=5 | OneDrive: last_seen=2024-05-20, first_seen=2022-07-03, confidence=medium, jobs=5 | LlamaIndex: last_seen=2026-06-07, first_seen=2024-07-29, confidence=medium, jobs=5 | Workday: last_seen=2026-06-12, first_seen=2024-10-17, confidence=medium, jobs=5 | Commvault: last_seen=2026-01-02, first_seen=2023-02-06, confidence=medium, jobs=5 | Azure Application Insights: last_seen=2026-06-10, first_seen=2025-09-18, confidence=medium, jobs=5 | Eloqua: last_seen=2023-12-20, first_seen=2022-10-05, confidence=medium, jobs=5 | Visual Studio: last_seen=2025-11-14, first_seen=2022-10-17, confidence=medium, jobs=5 | Genesys: last_seen=2026-01-31, first_seen=2023-11-02, confidence=medium, jobs=5 | Microsoft BitLocker: last_seen=2024-08-07, first_seen=2023-06-13, confidence=medium, jobs=4 | Veeam: last_seen=2023-05-13, first_seen=2022-10-05, confidence=medium, jobs=4 | NICE CXone: last_seen=2025-05-09, first_seen=2023-11-02, confidence=medium, jobs=4 | Concur: last_seen=2023-09-25, first_seen=2022-10-07, confidence=medium, jobs=4 | Azure Cost Management: last_seen=2026-06-09, first_seen=2025-09-12, confidence=medium, jobs=4 | Tradeshift: last_</t>
+          <t>Python: last_seen=2026-06-19, first_seen=2025-11-13, confidence=high, jobs=51 | Microsoft Excel: last_seen=2026-06-16, first_seen=2025-11-18, confidence=high, jobs=24 | Jira: last_seen=2026-06-17, first_seen=2025-11-27, confidence=high, jobs=14 | React: last_seen=2026-06-09, first_seen=2025-11-18, confidence=high, jobs=13 | Power BI: last_seen=2026-06-18, first_seen=2025-11-14, confidence=high, jobs=12 | Provide Support: last_seen=2026-06-15, first_seen=2025-11-14, confidence=high, jobs=10 | Docker: last_seen=2026-06-19, first_seen=2025-11-14, confidence=high, jobs=10 | Apache Hadoop: last_seen=2026-06-15, first_seen=2025-11-21, confidence=high, jobs=10 | Hadoop: last_seen=2026-06-15, first_seen=2025-11-21, confidence=high, jobs=10 | Streamline: last_seen=2026-06-09, first_seen=2025-11-14, confidence=high, jobs=9 | TypeScript: last_seen=2026-06-09, first_seen=2025-11-18, confidence=high, jobs=9 | Microsoft Forefront: last_seen=2026-06-19, first_seen=2025-11-14, confidence=high, jobs=8 | Confluence: last_seen=2026-06-15, first_seen=2025-11-27, confidence=high, jobs=8 | Redis: last_seen=2026-06-19, first_seen=2025-11-16, confidence=high, jobs=6 | Figma: last_seen=2026-06-15, first_seen=2025-11-13, confidence=high, jobs=6 | Zoom: last_seen=2026-06-17, first_seen=2025-12-05, confidence=high, jobs=6 | Apache Spark: last_seen=2026-06-15, first_seen=2025-11-15, confidence=high, jobs=6 | Elastic: last_seen=2026-06-09, first_seen=2026-04-13, confidence=high, jobs=5 | ChatGPT: last_seen=2026-06-19, first_seen=2026-04-06, confidence=high, jobs=5 | Claude by Anthropic: last_seen=2026-06-19, first_seen=2026-04-06, confidence=high, jobs=5 | Microsoft Powerpoint: last_seen=2026-06-15, first_seen=2025-11-13, confidence=high, jobs=5 | Kafka: last_seen=2026-06-19, first_seen=2025-11-16, confidence=high, jobs=5 | iOS: last_seen=2026-06-17, first_seen=2025-12-16, confidence=high, jobs=5 | Thrive: last_seen=2026-05-13, first_seen=2025-11-15, confidence=high, jobs=4 | Postman: last_seen=2026-06-02, first_seen=2025-12-02, confidence=high, jobs=4 | PyTorch: last_seen=2026-06-16, first_seen=2025-11-14, confidence=high, jobs=4 | n8n: last_seen=2026-05-04, first_seen=2026-04-13, confidence=high, jobs=4 | GitHub Copilot: last_seen=2026-06-19, first_seen=2026-04-17, confidence=high, jobs=3 | Materialize: last_seen=2026-06-09, first_seen=2025-11-14, confidence=high, jobs=3 | Workspace: last_seen=2026-06-09, first_seen=2025-12-05, confidence=high, jobs=3 | GitHub: last_seen=2026-06-19, first_seen=2026-04-17, confidence=high, jobs=3 | Qlik Sense: last_seen=2026-05-20, first_seen=2025-12-10, confidence=high, jobs=3 | Google Workspace: last_seen=2026-06-09, first_seen=2025-12-05, confidence=high, jobs=3 | NGINX: last_seen=2026-06-10, first_seen=2025-11-14, confidence=high, jobs=3 | Webpack: last_seen=2026-05-23, first_seen=2025-11-20, confidence=high, jobs=2 | Configure.IT: last_seen=2026-06-10, first_seen=2026-03-10, confidence=high, jobs=2 | Testrail: last_seen=2026-06-02, first_seen=2026-03-31, confidence=high, jobs=2 | Weex: last_seen=2026-04-19, first_seen=2025-11-20, confidence=high, jobs=1 | Next.js: last_seen=2026-05-23, first_seen=2025-12-02, confidence=high, jobs=1 | Flutter: last_seen=2026-04-19, first_seen=2025-11-20, confidence=high, jobs=1 | Babel: last_seen=2026-04-19, first_seen=2025-11-20, confidence=high, jobs=1 | Tailwind: last_seen=2026-05-23, first_seen=2025-12-02, confidence=high, jobs=1 | react-testing-library: last_seen=2026-05-23, first_seen=2025-12-02, confidence=high, jobs=1 | Monte Carlo: last_seen=2026-06-13, first_seen=2026-04-10, confidence=high, jobs=1 | Alteryx: last_seen=2026-04-02, first_seen=2026-01-28, confidence=high, jobs=1 | Storybook: last_seen=2026-05-23, first_seen=2025-12-02, confidence=high, jobs=1 | Chakra UI: last_seen=2026-05-23, first_seen=2025-12-02, confidence=high, jobs=1 | Java: last_seen=2026-06-19, first_seen=2025-11-16, confidence=medium, jobs=19 | JavaScript: last_seen=2026-06-09, first_seen=2025-11-18, confidence=medium, jobs=18 | Golang: last_seen=2026-06-19, first_seen=2025-11-13, confidence=medium, jobs=18 | Mac OS: last_seen=2026-06-17, first_seen=2025-11-21, confidence=medium, jobs=14 | macOS: last_seen=2026-06-17, first_seen=2025-11-21, confidence=medium, jobs=14 | Windows Server: last_seen=2026-06-17, first_seen=2025-11-21, confidence=medium, jobs=11 | Microsoft TypeScript: last_seen=2026-06-09, first_seen=2025-11-18, confidence=medium, jobs=9 | Microsoft Windows Server: last_seen=2026-06-17, first_seen=2025-11-21, confidence=medium, jobs=9 | MySQL: last_seen=2026-06-19, first_seen=2025-11-13, confidence=medium, jobs=8 | Scala: last_seen=2026-06-15, first_seen=2025-11-21, confidence=medium, jobs=7 | Tableau: last_seen=2026-06-05, first_seen=2025-11-14, confidence=medium, jobs=7 | C++: last_seen=2026-06-04, first_seen=2025-11-16, confidence=medium, jobs=5 | Kubernetes: last_seen=2026-06-19, first_seen=2025-11-16, confidence=medium, jobs=5 | Trello: last_seen=2026-05-25, first_seen=2025-11-27, confidence=medium, jobs=5 | Microsoft Active Directory: last_seen=2026-06-09, first_seen=2025-12-08, confidence=medium, jobs=4 | Flask: last_seen=2026-05-17, first_seen=2025-11-24, confidence=medium, jobs=4 | FastAPI: last_seen=2026-05-17, first_seen=2025-11-24, confidence=medium, jobs=4 | Active Directory: last_seen=2026-06-09, first_seen=2025-12-08, confidence=medium, jobs=4 | Node.js: last_seen=2026-05-17, first_seen=2025-11-24, confidence=medium, jobs=4 | PySpark: last_seen=2026-06-15, first_seen=2025-11-21, confidence=medium, jobs=3 | eLearning LMS: last_seen=2026-06-01, first_seen=2025-11-18, confidence=medium, jobs=3 | ServiceNow.com: last_seen=2026-06-17, first_seen=2025-12-19, confidence=medium, jobs=3 | Cypress: last_seen=2026-06-02, first_seen=2025-12-02, confidence=medium, jobs=3 | Qlik: last_seen=2026-05-20, first_seen=2025-12-10, confidence=medium, jobs=3 | Jenkins: last_seen=2026-06-01, first_seen=2025-11-13, confidence=medium, jobs=2 | CrowdStrike: last_seen=2026-06-09, first_seen=2026-04-21, confidence=medium, jobs=2 | LiveStream: last_seen=2026-06-02, first_seen=2026-03-31, confidence=medium, jobs=2 | Scale.ai: last_seen=2026-06-18, first_seen=2025-12-22, confidence=medium, jobs=2 | Selenium: last_seen=2026-06-02, first_seen=2026-04-20, confidence=medium, jobs=2 | GitLab: last_seen=2026-06-01, first_seen=2025-11-13, confidence=medium, jobs=2 | Playwright: last_seen=2026-06-02, first_seen=2026-04-20, confidence=medium, jobs=2 | Charles: last_seen=2026-05-23, first_seen=2025-12-02, confidence=medium, jobs=2 | TensorFlow: last_seen=2026-06-16, first_seen=2025-11-14, confidence=medium, jobs=2 | Freshservice: last_seen=2026-06-17, first_seen=2025-12-19, confidence=medium, jobs=2 | Jira Service Desk: last_seen=2026-06-17, first_seen=2025-12-19, confidence=medium, jobs=2 | CrowdStrike Falcon: last_seen=2026-06-09, first_seen=2026-04-21, confidence=medium, jobs=2 | Oracle: last_seen=2026-05-13, first_seen=2025-11-13, confidence=medium, jobs=2 | pytest: last_seen=2026-06-02, first_seen=2026-04-20, confidence=medium, jobs=2 | REST Client: last_seen=2026-06-02, first_seen=2026-04-20, confidence=medium, jobs=1 | Microsoft Graph: last_seen=2026-05-17, first_seen=2025-11-27, confidence=medium, jobs=1 | GuardRails: last_seen=2026-06-05, first_seen=2026-03-12, confidence=medium, jobs=1 | Kibana: last_seen=2026-01-14, first_seen=2025-12-01, confidence=medium, jobs=1 | Beats: last_seen=2026-02-08, first_seen=2025-12-27, confidence=medium, jobs=1 | Vite: last_seen=2026-05-23, first_seen=2025-12-02, confidence=medium, jobs=1 | Zustand: last_seen=2026-05-23, first_seen=2025-12-02, confidence=medium, jobs=1 | Google Cloud Platform: last_seen=2026-06-19, first_seen=2026-04-17, confidence=medium, jobs=1 | Cursor: last_seen=2026-06-09, first_seen=2026-04-06, confidence=medium, jobs=1 | Amazon Web Services: last_seen=2026-06-19, first_seen=2026-04-17, confidence=medium, jobs=1 | MUI: last_seen=2026-05-23, first_seen=2025-12-02, confidence=medium, jobs=1 | Gmail: last_seen=2026-06-09, first_seen=2026-05-11, confidence=medium, jobs=1 | Amazon Cloud Directory: last_seen=2026-06-09, first_seen=2026-05-11, confidence=medium, jobs=1 | Airflow: last_seen=2026-03-07, first_seen=2026-02-13, confidence=medium, jobs=1 | Datahub: last_seen=2025-12-28, first_seen=2025-11-15, confidence=medium, jobs=1 | Prettier: last_seen=2026-05-23, first_seen=2025-12-02, confidence=medium, jobs=1 | SBT: last_seen=2026-01-28, first_seen=2025-12-17, confidence=medium, jobs=1 | LangChain: last_seen=2026-05-11, first_seen=2025-11-19, confidence=medium, jobs=1 | Zoom Phone: last_seen=2026-06-09, first_seen=2026-05-11, confidence=medium, jobs=1 | Redux: last_seen=2026-05-23, first_seen=2025-12-02, confidence=medium, jobs=1 | ESLint: last_seen=2026-05-23, first_seen=2025-12-02, confidence=medium, jobs=1 | Veeam: last_seen=2026-06-09, first_seen=2026-06-09, confidence=medium, jobs=1 | LangGraph: last_seen=2026-05-11, first_seen=2025-11-19, confidence=medium, jobs=1 | Rollout: last_seen=2025-12-21, first_seen=2025-11-29, confidence=medium, jobs=1 | Built In: last_seen=2026-06-09, first_seen=2026-05-11, confidence=medium, jobs=1 | GraphQL: last_seen=2026-05-23, first_seen=2025-12-02, confidence=medium, jobs=1 | Elasticsearch: last_seen=2026-01-14, first_seen=2025-12-01, confidence=medium, jobs=1 | Splunk: last_seen=2026-04-30, first_seen=2026-04-30, confidence=medium, jobs=1 | Apache Airflow: last_seen=2026-03-07, first_seen=2026-02-13, confidence=medium, jobs=1 | Google Chrome: last_seen=2026-06-09, first_seen=2026-05-11, confidence=medium, jobs=1 | User Interviews: last_seen=2026-02-02, first_seen=2026-02-02, confidence=medium, jobs=1 | Zoom Rooms: last_seen=2026-06-09, first_seen=2026-05-11, confidence=medium, jobs=1 | Processing: last_seen=2026-05-20, first_seen=2026-01-19, confidence=low, jobs=4 | XML: last_seen=2026-04-30, first_seen=2025-11-16, confidence=low, jobs=2 | JSON: last_seen=2026-04-30, first_seen=2025-11-16, confidence=low, jobs=2 | Falcon: last_seen=2026-06-09, first_seen=2026-04-21, confidence=low, jobs=2 | Grafana: last_seen=2026-04-30, first_seen=2025-11-13, confidence=low, jobs=2 | Ansible: last_seen=2026-06-05, first_seen=2026-04-06, confidence=low, jobs=2 | CSS 3: last_seen=2026-05-23, first_seen=2025-12-02, confidence=low, jobs=1 | Hugging Face: last_seen=2025-11-18, first_seen=2025-11-18, confidence=low, jobs=1 | TalentLMS: last_seen=2026-02-16, first_seen=2026-01-26, confidence=low, jobs=1 | Swift: last_seen=2026-01-07, first_seen=2025-12-16, confidence=low, jobs=1 | Objective-C: last_seen=2026-01-07, first_seen=2025-12-16, confidence=low, jobs=1 | Kotlin: last_seen=2026-01-07, first_seen=2025-12-16, confidence=low, jobs=1 | HTML5: last_seen=2026-05-23, first_seen=2025-12-02, confidence=low, jobs=1 | Metabase: last_seen=2025-12-28, first_seen=2025-11-15, confidence=low, jobs=1 | Bridge: last_seen=2025-12-21, first_seen=2025-11-29, confidence=low, jobs=1 | OAuth: last_seen=2026-06-09, first_seen=2026-05-11, confidence=low, jobs=1 | Vue.js: last_seen=2026-04-19, first_seen=2025-11-20, confidence=low, jobs=1 | Jest: last_seen=2026-05-23, first_seen=2025-12-02, confidence=low, jobs=1 | FreshDesk: last_seen=2026-05-15, first_seen=2026-05-15, confidence=low, jobs=1 | Triton: last_seen=2026-06-13, first_seen=2026-04-10, confidence=low, jobs=1 | Prometheus: last_seen=2025-11-13, first_seen=2025-11-13, confidence=low, jobs=1 | Docker Swarm: last_seen=2026-01-14, first_seen=2025-12-01, confidence=low, jobs=1 | KNIME: last_seen=2026-04-02, first_seen=2026-01-28, confidence=low, jobs=1 | CUDA: last_seen=2026-06-13, first_seen=2026-04-10, confidence=low, jobs=1 | GitLab CI: last_seen=2026-06-01, first_seen=2026-04-20, confidence=low, jobs=1 | GitHub Actions: last_seen=2026-06-01, first_seen=2026-04-20, confidence=low, jobs=1 | Turning: last_seen=2026-06-02, first_seen=2026-06-02, confidence=low, jobs=1 | PostgreSQL: last_seen=2026-06-19, first_seen=2026-04-17, confidence=low, jobs=1 | RabbitMQ: last_seen=2026-06-19, first_seen=2026-04-17, confidence=low, jobs=1 | CentOS: last_seen=2026-06-03, first_seen=2026-01-26, confidence=low, jobs=1 | Ubuntu: last_seen=2026-06-03, first_seen=2026-01-26, confidence=low, jobs=1 | JUnit: last_seen=2026-06-01, first_seen=2026-04-20, confidence=low, jobs=1 | TestNG: last_seen=2026-06-01, first_seen=2026-04-20, confidence=low, jobs=1</t>
         </is>
       </c>
     </row>
